--- a/data/trending_integrated_20260910_13.xlsx
+++ b/data/trending_integrated_20260910_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3665</v>
+        <v>4145</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+83.25%</t>
+          <t>+107.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>689194000000</v>
+        <v>718740000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호, 합병 대상 업종(신재생에너지) 관련 기대감과 스팩 특유의 높은 변동성 예측.</t>
+          <t>스팩 합병 기대감 속에 급등 후 변동성 확대. 합병 대상 업종 관련 불확실성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신재생에너지', '스팩', '합병']</t>
+          <t>['스팩', '합병', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8190</v>
+        <v>8290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+43.43%</t>
+          <t>+45.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F3" t="n">
         <v>113</v>
       </c>
       <c r="G3" t="n">
-        <v>1360</v>
+        <v>1384</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>65847000000</v>
+        <v>66204000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -765,10 +765,10 @@
         <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
         <v>0.14</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼미금속, 그래핀 신소재 관련 호재 및 대규모 미국 투자 기대감에 따른 주가 급등 예상.</t>
+          <t>그래핀 신소재 호재 및 대규모 대미 투자 소식. 주가 급등 후 매물 출회.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '미국 투자']</t>
+          <t>['그래핀', '대미 투자', '호재']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14680</v>
+        <v>14620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.44%</t>
+          <t>+21.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F5" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G5" t="n">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>284501000000</v>
+        <v>285875000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>지정학적 리스크로 인한 유가 급등 전망과 함께 단기 급등 및 상한가 마감에 대한 기대감이 매우 높음.</t>
+          <t>이란발 지정학적 리스크 및 유가 급등에 따른 수혜 기대. 단기 급등 후 차익 실현 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '호르무즈']</t>
+          <t>['유가 급등', '지정학적 리스크', '차익 실현']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3615</v>
+        <v>14180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.90%</t>
+          <t>+20.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>599</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3015</v>
+        <v>11810</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="O6" t="n">
-        <v>24102000000</v>
+        <v>131027000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,60 +994,60 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>우리기술, 미국 신규 원전 건설 수주 기대감에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['원전', '수주', '미국 건설']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14020</v>
+        <v>3580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.71%</t>
+          <t>+18.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>611</v>
+        <v>63</v>
       </c>
       <c r="H7" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11810</v>
+        <v>3015</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>128867000000</v>
+        <v>24233000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1086,29 +1086,29 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>우리기술, 미국 신규 원전 건설 수주 기대감에 따른 주가 상승 전망.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '수주', '미국 건설']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13130</v>
+        <v>13090</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.88%</t>
+          <t>+13.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H8" t="n">
         <v>4.37</v>
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>95474000000</v>
+        <v>95892000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154800</v>
+        <v>154900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+12.17%</t>
+          <t>+12.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F9" t="n">
         <v>184</v>
       </c>
       <c r="G9" t="n">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
         <v>15.65</v>
@@ -1254,7 +1254,7 @@
         <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>361405000000</v>
+        <v>366067000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유가 상승에 따른 긍정적 전망과 함께 매수 기회라는 의견이 제시되나, 단기적인 상승에 대한 경계도 존재함.</t>
+          <t>유가 급등에 따른 기대감에도 불구하고 주가 하락. 외인 대량 매집과 주가 괴리.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유가', '매수']</t>
+          <t>['유가 급등', '기대감', '외국인 매집']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,39 +1299,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2120</v>
+        <v>1935</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+10.30%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>2.12</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1922</v>
+        <v>1760</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
-        <v>19457000000</v>
+        <v>187915000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,20 +1362,20 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>매집 및 수혜 기대감이 있으나, 구체적인 근거 제시 없이 개인적인 투자 판단에 의존하는 경향이 강함.</t>
+          <t>외국인 매수세 유입에도 불구하고 변동성이 큰 흐름. 기대감 속 단기 차익 실현 가능성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['외국인', '변동성', '차익 실현']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14450</v>
+        <v>14430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+9.90%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
         <v>116</v>
@@ -1438,7 +1438,7 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>114477000000</v>
+        <v>114976000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1483,39 +1483,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1931</v>
+        <v>2100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>+9.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="H12" t="n">
-        <v>2.12</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1760</v>
+        <v>1922</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>187199000000</v>
+        <v>19613000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>감정적인 언급과 개인적인 경험에 기반한 투자 의견이 주를 이루며, 객관적인 사실 기반 분석은 부족함.</t>
+          <t>매집 및 수혜 기대감이 있으나, 구체적인 근거 제시 없이 개인적인 투자 판단에 의존하는 경향이 강함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F13" t="n">
         <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="H13" t="n">
         <v>2.89</v>
@@ -1682,10 +1682,10 @@
         <v>0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
         <v>128</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>가온전선 상승 대비 대한전선 흐름 약세. 변동성 확대 및 차익 실현 가능성에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['변동성', '차익실현', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3860</v>
+        <v>3880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>+6.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>135218000000</v>
+        <v>136411000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 회피와 6G 테마에 대한 기대감으로 상승 전망이 있으나, 주가 변동성에 대한 우려도 있음.</t>
+          <t>투기과열종목 지정 회피 및 6G 통신 이슈. 긍정적인 뉴스 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['6G', '광통신']</t>
+          <t>['투기과열', '6G', '통신']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6810</v>
+        <v>6780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+5.91%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
         <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="H16" t="n">
         <v>15.68</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>13907000000</v>
+        <v>14334000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스, 로봇/반도체 사업 기대감에도 불구하고 외인 매도 및 주가 흐름에 대한 부정적 의견.</t>
+          <t>한화 그룹주로서의 기대감 존재하나, 외국인 매도세 및 주가 부진 지속. 분사 이슈.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇', '반도체', '외인 매도']</t>
+          <t>['한화', '외국인 매도', '분사']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F17" t="n">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G17" t="n">
-        <v>1980</v>
+        <v>2014</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G18" t="n">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G19" t="n">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>신규주 상승 가능성 언급되나, 프로그램 매매와 계단식 하락 패턴 관찰. 급락 및 매도 의견 다수.</t>
+          <t>급락 후 반등했으나, 급락 우려와 함께 매도 의견 다수. 좋은 재료에도 상승폭 제한적이라는 의견.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['신규주', '급락', '프로그램']</t>
+          <t>['주포', '급락', '재료']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H20" t="n">
         <v>7.54</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
+          <t>자사주 매입 및 소각을 통한 주주환원 기대감 상승. 샘표와 비교하며 소각 규모 및 비율에 대한 논의.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['소각', '주주환원', '자사주']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15640</v>
+        <v>2170</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="E21" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>434</v>
+        <v>178</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15650</v>
+        <v>2160</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>6327000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2374,20 +2374,20 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>금호건설, 수주 기사 및 긍정적 실적 전망에도 불구하고 주가 부진 및 개미 투자자 주의 요구.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '실적', '주가 부진']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,46 +2396,46 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>267250</v>
+        <v>248</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>791</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>471</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>1307</v>
+        <v>121</v>
       </c>
       <c r="H22" t="n">
-        <v>46.81</v>
+        <v>5.86</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269500</v>
+        <v>248</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>46.85</v>
+        <v>6.18</v>
       </c>
       <c r="O22" t="n">
-        <v>2203737000000</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,60 +2466,60 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼성전자, 자사주 15조 매수 희소식에도 불구하고 외인 매도세 및 악재 누적으로 인한 하락세 전망.</t>
+          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매수', '악재', '외인 매도']</t>
+          <t>['상폐', '시가총액', '허매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2140</v>
+        <v>15640</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G23" t="n">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2160</v>
+        <v>15650</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6237000000</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,20 +2558,20 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>써니전자, 유증 및 M&amp;A 관련 불확실성 속에서 주가 변동성 예상.</t>
+          <t>수주 공시에도 불구하고 주가 부진. 시장 전반의 부정적 심리 및 건설업종 약세.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['유증', 'M&amp;A', '주가 변동성']</t>
+          <t>['수주', '공시', '건설업']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18960</v>
+        <v>267250</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.06%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>108</v>
+        <v>794</v>
       </c>
       <c r="F24" t="n">
-        <v>64</v>
+        <v>474</v>
       </c>
       <c r="G24" t="n">
-        <v>370</v>
+        <v>1315</v>
       </c>
       <c r="H24" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>19970</v>
+        <v>269500</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>79809000000</v>
+        <v>2257003000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 투자 기대감과 대차해지 운동 동참 호소. 주주들의 적극적인 참여 독려.</t>
+          <t>삼성전자, 자사주 15조 매수 희소식에도 불구하고 외인 매도세 및 악재 누적으로 인한 하락세 전망.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['미국 투자', '대차해지', '주주']</t>
+          <t>['자사주 매수', '악재', '외인 매도']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,46 +2672,46 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3655</v>
+        <v>18880</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.04%</t>
+          <t>-5.46%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>151</v>
+        <v>381</v>
       </c>
       <c r="H25" t="n">
-        <v>1.54</v>
+        <v>10.64</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3890</v>
+        <v>19970</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>48129000000</v>
+        <v>81692000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,60 +2742,60 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>대차 해지 운동 동참 요구가 높으나, 주가는 큰 폭 하락. 매도세와 대차 잔고 이슈 복합 작용.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['대차 해지', '하락', '매도세']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>523</v>
+        <v>3640</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-13.84%</t>
+          <t>-6.43%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.38</v>
+        <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>1.54</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>607</v>
+        <v>3890</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>8167000000</v>
+        <v>48310000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -2878,13 +2878,13 @@
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H27" t="n">
         <v>0.07000000000000001</v>
@@ -2955,31 +2955,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>135</v>
+        <v>520</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-45.56%</t>
+          <t>-14.33%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.32</v>
+        <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="H28" t="n">
-        <v>5.86</v>
+        <v>2.8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>248</v>
+        <v>607</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.18</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>871000000</v>
+        <v>8215000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['상폐', '시가총액', '허매수']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>033340</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_13.xlsx
+++ b/data/trending_integrated_20260910_13.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4145</v>
+        <v>4215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+107.25%</t>
+          <t>+110.75%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>460</v>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>718740000000</v>
+        <v>735038000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8290</v>
+        <v>8200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+45.18%</t>
+          <t>+43.61%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G3" t="n">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>66204000000</v>
+        <v>66357000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -762,13 +762,13 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
         <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H4" t="n">
         <v>0.14</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>그래핀 신소재 호재 및 대규모 대미 투자 소식. 주가 급등 후 매물 출회.</t>
+          <t>그래핀 등 신소재 관련 호재 언급 있으나, 주가 하락 의견과 혼재. 변동성 큼.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['그래핀', '대미 투자', '호재']</t>
+          <t>['그래핀', '신소재', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14620</v>
+        <v>14560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.93%</t>
+          <t>+21.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F5" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G5" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>285875000000</v>
+        <v>286281000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크 및 유가 급등에 따른 수혜 기대. 단기 급등 후 차익 실현 가능성.</t>
+          <t>중동 유가 급등 및 전쟁 심화 관련하여 주가 상승 기대감 있으나, 변동성 큼.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가 급등', '지정학적 리스크', '차익 실현']</t>
+          <t>['유가', '중동', '급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14180</v>
+        <v>14170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+20.07%</t>
+          <t>+19.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="H6" t="n">
         <v>6.09</v>
@@ -978,7 +978,7 @@
         <v>5.64</v>
       </c>
       <c r="O6" t="n">
-        <v>131027000000</v>
+        <v>131521000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3580</v>
+        <v>3590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.74%</t>
+          <t>+19.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24233000000</v>
+        <v>24282000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13090</v>
+        <v>13020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.53%</t>
+          <t>+12.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
         <v>46</v>
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>95892000000</v>
+        <v>95998000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154900</v>
+        <v>155200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+12.25%</t>
+          <t>+12.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F9" t="n">
         <v>184</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H9" t="n">
         <v>15.65</v>
@@ -1254,7 +1254,7 @@
         <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>366067000000</v>
+        <v>366801000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1935</v>
+        <v>1925</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+9.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H10" t="n">
         <v>2.12</v>
@@ -1346,7 +1346,7 @@
         <v>2.07</v>
       </c>
       <c r="O10" t="n">
-        <v>187915000000</v>
+        <v>188081000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14430</v>
+        <v>14360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.90%</t>
+          <t>+9.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H11" t="n">
         <v>0.57</v>
@@ -1438,7 +1438,7 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>114976000000</v>
+        <v>115295000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감이 있으나, 중동 관련 사업과의 연관성에 대한 혼란과 확인되지 않은 정보가 혼재함.</t>
+          <t>중동 관련 수출 기업으로 언급, 재무제표 기반 긍정 전망 있으나 주가 변동성 큼.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['재무제표', '수출', '중동']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2100</v>
+        <v>14960</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+9.26%</t>
+          <t>+9.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>1.34</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
-        <v>234</v>
+        <v>477</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>2.89</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1922</v>
+        <v>13700</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.51</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>19613000000</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,20 +1546,20 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>매집 및 수혜 기대감이 있으나, 구체적인 근거 제시 없이 개인적인 투자 판단에 의존하는 경향이 강함.</t>
+          <t>미국 광통신 섹터 강세 및 AI 관련주로 묶이며 상승 기대감 높음. 긍정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['광통신', 'AI', '상승']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14960</v>
+        <v>2090</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+9.20%</t>
+          <t>+8.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.34</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>471</v>
+        <v>237</v>
       </c>
       <c r="H13" t="n">
-        <v>2.89</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13700</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>0.51</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>19695000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신 및 AI 관련주 강세에 따른 수혜 기대감으로 주가 상승 전망.</t>
+          <t>테마주로서의 수혜 및 매집 관련 언급. 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '미국 시장']</t>
+          <t>['테마주', '매집']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H14" t="n">
         <v>12.31</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3880</v>
+        <v>3895</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.59%</t>
+          <t>+7.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>136411000000</v>
+        <v>136965000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 및 6G 통신 이슈. 긍정적인 뉴스 기반 상승 기대.</t>
+          <t>투기과열종목 지정 회피 및 광통신 사업 관련 긍정적 언급. 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투기과열', '6G', '통신']</t>
+          <t>['광통신', '투기과열', '상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6780</v>
+        <v>6760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+5.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H16" t="n">
         <v>15.68</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>14334000000</v>
+        <v>14494000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G17" t="n">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SK하이닉스, 전반적인 시장 강세 속에서 반등 기대감 존재하나, 주가 변동성에 대한 의견 분분.</t>
+          <t>대세 상승 추세에 대한 기대감과 함께 단기적인 하락 및 급등 가능성 언급. 근거 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반도체', '시장 강세', '주가 변동성']</t>
+          <t>['대세 상승', '단기 급등']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F18" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G18" t="n">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
+          <t>미국 원전 건설 및 웨스팅하우스 인수 관련 호재 언급. 상승 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '호재']</t>
+          <t>['원전', '미국', '호재']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F19" t="n">
         <v>103</v>
       </c>
       <c r="G19" t="n">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>급락 후 반등했으나, 급락 우려와 함께 매도 의견 다수. 좋은 재료에도 상승폭 제한적이라는 의견.</t>
+          <t>신규 상장주로서 급락 및 매도 의견 다수. 재료 대비 주가 흐름 부진.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주포', '급락', '재료']</t>
+          <t>['신규주', '급락', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2311,39 +2311,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2170</v>
+        <v>248</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="H21" t="n">
-        <v>4.91</v>
+        <v>5.86</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2160</v>
+        <v>248</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.26</v>
+        <v>6.18</v>
       </c>
       <c r="O21" t="n">
-        <v>6327000000</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['상폐', '시가총액', '허매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,51 +2391,51 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>248</v>
+        <v>15640</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="G22" t="n">
-        <v>121</v>
+        <v>451</v>
       </c>
       <c r="H22" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>248</v>
+        <v>15650</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2466,60 +2466,60 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
+          <t>수주 공시에도 불구하고 주가 부진. 시장 전반의 부정적 심리 및 건설업종 약세.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['상폐', '시가총액', '허매수']</t>
+          <t>['수주', '공시', '건설업']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15640</v>
+        <v>2145</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>447</v>
+        <v>178</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15650</v>
+        <v>2160</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6373000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,20 +2558,20 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>수주 공시에도 불구하고 주가 부진. 시장 전반의 부정적 심리 및 건설업종 약세.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주', '공시', '건설업']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>267250</v>
+        <v>267500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="F24" t="n">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G24" t="n">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="H24" t="n">
         <v>46.81</v>
@@ -2634,7 +2634,7 @@
         <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>2257003000000</v>
+        <v>2271122000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>삼성전자, 자사주 15조 매수 희소식에도 불구하고 외인 매도세 및 악재 누적으로 인한 하락세 전망.</t>
+          <t>명확한 근거 없이 주가 하락 및 매도 의견 다수.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['자사주 매수', '악재', '외인 매도']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18880</v>
+        <v>18870</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.46%</t>
+          <t>-5.51%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F25" t="n">
         <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>81692000000</v>
+        <v>82113000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2775,11 +2775,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3640</v>
+        <v>3635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.43%</t>
+          <t>-6.56%</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>48310000000</v>
+        <v>48516000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2959,18 +2959,18 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-14.33%</t>
+          <t>-14.99%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F28" t="n">
         <v>30</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>8215000000</v>
+        <v>8255000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260910_13.xlsx
+++ b/data/trending_integrated_20260910_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4215</v>
+        <v>4290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+110.75%</t>
+          <t>+114.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G2" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>735038000000</v>
+        <v>746456000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스팩 합병 기대감 속에 급등 후 변동성 확대. 합병 대상 업종 관련 불확실성.</t>
+          <t>합병 관련 업종 언급 있으나, 주가 흐름에 대한 기대와 우려가 혼재. 구체적인 사실 근거 부족.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩', '합병', '변동성']</t>
+          <t>['스팩', '합병', '주가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8200</v>
+        <v>8240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+43.61%</t>
+          <t>+44.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>264</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>66357000000</v>
+        <v>66480000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
         <v>101</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14560</v>
+        <v>14450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.43%</t>
+          <t>+20.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G5" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>286281000000</v>
+        <v>288030000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14170</v>
+        <v>14100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.98%</t>
+          <t>+19.39%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="H6" t="n">
         <v>6.09</v>
@@ -978,7 +978,7 @@
         <v>5.64</v>
       </c>
       <c r="O6" t="n">
-        <v>131521000000</v>
+        <v>132198000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3590</v>
+        <v>3555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+19.07%</t>
+          <t>+17.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24282000000</v>
+        <v>24385000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13020</v>
+        <v>155400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.92%</t>
+          <t>+12.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>405</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="G8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>4.37</v>
+        <v>15.65</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11530</v>
+        <v>138000</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.63</v>
+        <v>15.25</v>
       </c>
       <c r="O8" t="n">
-        <v>95998000000</v>
+        <v>368993000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>유가 급등에 따른 기대감에도 불구하고 주가 하락. 외인 대량 매집과 주가 괴리.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['유가 급등', '기대감', '외국인 매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155200</v>
+        <v>12860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+12.46%</t>
+          <t>+11.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E9" t="n">
-        <v>401</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>184</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>993</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
-        <v>15.65</v>
+        <v>4.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138000</v>
+        <v>11530</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>15.25</v>
+        <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>366801000000</v>
+        <v>96281000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유가 급등에 따른 기대감에도 불구하고 주가 하락. 외인 대량 매집과 주가 괴리.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유가 급등', '기대감', '외국인 매집']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1925</v>
+        <v>14440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.38%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="H10" t="n">
-        <v>2.12</v>
+        <v>0.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1760</v>
+        <v>13130</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>188081000000</v>
+        <v>115623000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입에도 불구하고 변동성이 큰 흐름. 기대감 속 단기 차익 실현 가능성.</t>
+          <t>중동 관련 수출 기업으로 언급, 재무제표 기반 긍정 전망 있으나 주가 변동성 큼.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외국인', '변동성', '차익 실현']</t>
+          <t>['재무제표', '수출', '중동']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14360</v>
+        <v>1924</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.37%</t>
+          <t>+9.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.53</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="G11" t="n">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="H11" t="n">
-        <v>0.57</v>
+        <v>2.12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13130</v>
+        <v>1760</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>115295000000</v>
+        <v>188655000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>중동 관련 수출 기업으로 언급, 재무제표 기반 긍정 전망 있으나 주가 변동성 큼.</t>
+          <t>외국인 매수세 지속에도 불구하고 주가 변동성이 큰 상황. 향후 주가 흐름에 대한 기대감 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['재무제표', '수출', '중동']</t>
+          <t>['외국인', '변동성', '기대감']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>092790</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>1.34</v>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="H12" t="n">
         <v>2.89</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세 및 AI 관련주로 묶이며 상승 기대감 높음. 긍정적 전망.</t>
+          <t>미국 광통신 및 반도체 강세와 함께 주가 상승 기대감 높음. 외국인 매수세 유입 확인, 추세 전환 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '상승']</t>
+          <t>['광통신', '반도체', '외국인 매수', '추세']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,39 +1575,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2090</v>
+        <v>31100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.74%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
+        <v>12.31</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>28750</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.51</v>
+        <v>12.14</v>
       </c>
       <c r="O13" t="n">
-        <v>19695000000</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>테마주로서의 수혜 및 매집 관련 언급. 명확한 근거 부족.</t>
+          <t>가온전선 상승 대비 대한전선 흐름 약세. 변동성 확대 및 차익 실현 가능성에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['테마주', '매집']</t>
+          <t>['변동성', '차익실현', '주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,46 +1660,46 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31100</v>
+        <v>2070</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+7.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="H14" t="n">
-        <v>12.31</v>
+        <v>0.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>28750</v>
+        <v>1922</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12.14</v>
+        <v>0.51</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>19794000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>가온전선 상승 대비 대한전선 흐름 약세. 변동성 확대 및 차익 실현 가능성에 대한 부정적 전망.</t>
+          <t>주가 상승에 대한 기대감과 함께 매집 관련 언급. 새만금, 반도체 등 테마 언급 있으나 구체적 근거는 미흡.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['변동성', '차익실현', '주가']</t>
+          <t>['매집', '주가 상승', '테마']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3895</v>
+        <v>3880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+7.01%</t>
+          <t>+6.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>136965000000</v>
+        <v>137600000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 및 광통신 사업 관련 긍정적 언급. 상승 기대.</t>
+          <t>투기과열종목 지정 회피 관련 언급과 함께 주가 상승에 대한 기대감 존재. 5G/6G 등 관련 이슈 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '투기과열', '상승']</t>
+          <t>['투경 회피', '주가 상승', '이슈']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6760</v>
+        <v>6820</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+5.13%</t>
+          <t>+6.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H16" t="n">
         <v>15.68</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>14494000000</v>
+        <v>14729000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1856000</v>
+        <v>1846000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+3.51%</t>
+          <t>+2.96%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F17" t="n">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G17" t="n">
-        <v>2023</v>
+        <v>2050</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -1990,7 +1990,7 @@
         <v>50.66</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3957607000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대세 상승 추세에 대한 기대감과 함께 단기적인 하락 및 급등 가능성 언급. 근거 부족.</t>
+          <t>주가 상승에 대한 기대감이 높으며, 외인 매도와 관계없이 상승 추세를 예상하는 의견 다수. 일부 조정 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대세 상승', '단기 급등']</t>
+          <t>['상승 기대', '조정', '외인']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,10 +2050,10 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F18" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G18" t="n">
         <v>810</v>
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F19" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G19" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>신규 상장주로서 급락 및 매도 의견 다수. 재료 대비 주가 흐름 부진.</t>
+          <t>주가 급락에 대한 부정적 언급과 함께 '나락 차트', '축제 끝' 등 강한 부정적 표현 다수. 매도 의견 우세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['신규주', '급락', '매도']</t>
+          <t>['급락', '매도', '부정적']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,10 +2234,10 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
         <v>111</v>
@@ -2332,7 +2332,7 @@
         <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H21" t="n">
         <v>5.86</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>수주 공시에도 불구하고 주가 부진. 시장 전반의 부정적 심리 및 건설업종 약세.</t>
+          <t>수주 기사 관련 언급 있으나 시장 반응 미미. 주가 상승 기대와 함께 담는 것이 좋다는 의견 존재. 구체적 사실 근거는 제한적.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['수주', '공시', '건설업']</t>
+          <t>['수주', '주가 상승', '기대']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2542,7 +2542,7 @@
         <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>6373000000</v>
+        <v>6394000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>267500</v>
+        <v>267000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="F24" t="n">
         <v>470</v>
       </c>
       <c r="G24" t="n">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="H24" t="n">
         <v>46.81</v>
@@ -2634,7 +2634,7 @@
         <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>2271122000000</v>
+        <v>2283898000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>명확한 근거 없이 주가 하락 및 매도 의견 다수.</t>
+          <t>정치적 언급이 주를 이루며, 삼성전자 자체에 대한 분석이나 전망은 미미. 자사주 매수 관련 긍정적 언급 소수 존재.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['자사주 매수', '정치']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18870</v>
+        <v>18900</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>-5.36%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>82113000000</v>
+        <v>83555000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차 해지 운동 동참 요구가 높으나, 주가는 큰 폭 하락. 매도세와 대차 잔고 이슈 복합 작용.</t>
+          <t>대차 해지 운동 관련 언급이 압도적. 주가 상승에 대한 기대감이 반영되었으나, 근거는 대차 해지에 집중.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차 해지', '하락', '매도세']</t>
+          <t>['대차 해지', '주주 운동', '상승 기대']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2786,7 +2786,7 @@
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
         <v>42</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>48516000000</v>
+        <v>48737000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2959,11 +2959,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-14.99%</t>
+          <t>-15.16%</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>8255000000</v>
+        <v>8299000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260910_13.xlsx
+++ b/data/trending_integrated_20260910_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4290</v>
+        <v>4630</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+114.50%</t>
+          <t>+131.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>469</v>
+        <v>504</v>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>746456000000</v>
+        <v>799352000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8240</v>
+        <v>8120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+44.31%</t>
+          <t>+42.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G3" t="n">
-        <v>1388</v>
+        <v>1418</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>66480000000</v>
+        <v>67504000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 폐암 치료제 관련 글로벌 제약사 협력 및 임상 결과 발표 임박에 따른 강한 상승 기대.</t>
+          <t>페니트리움바이오, 폐암 학회 참여 및 다락손 관련 신규 임상 기대감. 글로벌 제약사 협력 및 대규모 재료.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['폐암 치료제', '임상', '글로벌 협력']</t>
+          <t>['폐암 학회', '다락손', '신규 임상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H4" t="n">
         <v>0.14</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14450</v>
+        <v>14540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+20.52%</t>
+          <t>+21.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F5" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G5" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>288030000000</v>
+        <v>289390000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중동 유가 급등 및 전쟁 심화 관련하여 주가 상승 기대감 있으나, 변동성 큼.</t>
+          <t>흥구석유, 중동 유가 급등 및 유조선 피격 관련 상승 기대. 단기 변동성 속 거래량 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '중동', '급등']</t>
+          <t>['유가 급등', '유조선 피격', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14100</v>
+        <v>14195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.39%</t>
+          <t>+20.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H6" t="n">
         <v>6.09</v>
@@ -978,7 +978,7 @@
         <v>5.64</v>
       </c>
       <c r="O6" t="n">
-        <v>132198000000</v>
+        <v>133739000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>우리기술, 미국 신규 원전 건설 수주 기대감에 따른 주가 상승 전망.</t>
+          <t>우리기술, 원전주로서 미국 신규 건설 및 공매도 금지 관련 긍정적 전망. 2만 원 목표 및 양전 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '수주', '미국 건설']</t>
+          <t>['원전주', '신규 건설', '공매도 금지']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3555</v>
+        <v>3560</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+17.91%</t>
+          <t>+18.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24385000000</v>
+        <v>24618000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>155400</v>
+        <v>154600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.61%</t>
+          <t>+12.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F8" t="n">
         <v>184</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="H8" t="n">
         <v>15.65</v>
@@ -1162,7 +1162,7 @@
         <v>15.25</v>
       </c>
       <c r="O8" t="n">
-        <v>368993000000</v>
+        <v>373582000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유가 급등에 따른 기대감에도 불구하고 주가 하락. 외인 대량 매집과 주가 괴리.</t>
+          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가 급등', '기대감', '외국인 매집']</t>
+          <t>['유가 폭등', '매집', '단기 차별화']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12860</v>
+        <v>12910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.54%</t>
+          <t>+11.97%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" t="n">
         <v>4.37</v>
@@ -1254,7 +1254,7 @@
         <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>96281000000</v>
+        <v>96659000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14440</v>
+        <v>14360</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>+9.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H10" t="n">
         <v>0.57</v>
@@ -1346,7 +1346,7 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>115623000000</v>
+        <v>116287000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>중동 관련 수출 기업으로 언급, 재무제표 기반 긍정 전망 있으나 주가 변동성 큼.</t>
+          <t>넥스틸, 중동 수출 가능성 언급 및 재무제표 기반 목표가 제시. 단기 변동성 후 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['재무제표', '수출', '중동']</t>
+          <t>['중동 수출', '재무제표', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,39 +1391,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1924</v>
+        <v>14960</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.32%</t>
+          <t>+9.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>1.34</v>
       </c>
       <c r="E11" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>173</v>
+        <v>518</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>2.89</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1760</v>
+        <v>13700</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>188655000000</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,20 +1454,20 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 매수세 지속에도 불구하고 주가 변동성이 큰 상황. 향후 주가 흐름에 대한 기대감 존재.</t>
+          <t>미국 광통신 섹터 강세에 따른 기대감. AI 관련주로 분류.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외국인', '변동성', '기대감']</t>
+          <t>['광통신', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,46 +1476,46 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14960</v>
+        <v>1917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+9.20%</t>
+          <t>+8.92%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.34</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>493</v>
+        <v>174</v>
       </c>
       <c r="H12" t="n">
-        <v>2.89</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13700</v>
+        <v>1760</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>189708000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,20 +1546,20 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 및 반도체 강세와 함께 주가 상승 기대감 높음. 외국인 매수세 유입 확인, 추세 전환 전망.</t>
+          <t>외국인 매수세 지속에도 불구하고 주가 변동성이 큰 상황. 향후 주가 흐름에 대한 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '반도체', '외국인 매수', '추세']</t>
+          <t>['외국인', '변동성', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,46 +1568,46 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31100</v>
+        <v>2080</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+8.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>132</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>12.31</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>28750</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>12.14</v>
+        <v>0.51</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>19885000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>가온전선 상승 대비 대한전선 흐름 약세. 변동성 확대 및 차익 실현 가능성에 대한 부정적 전망.</t>
+          <t>강동씨앤엘, 새만금 및 반도체 테마 수혜 기대감 속 매집 흐름. 상한가 및 바닥 매수 권유.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['변동성', '차익실현', '주가']</t>
+          <t>['새만금', '반도체 테마', '매집']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,46 +1660,46 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2070</v>
+        <v>31100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.70%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85</v>
+        <v>12.31</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>28750</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.51</v>
+        <v>12.14</v>
       </c>
       <c r="O14" t="n">
-        <v>19794000000</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 함께 매집 관련 언급. 새만금, 반도체 등 테마 언급 있으나 구체적 근거는 미흡.</t>
+          <t>가온전선 상승 대비 대한전선 흐름 약세. 변동성 확대 및 차익 실현 가능성에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['매집', '주가 상승', '테마']</t>
+          <t>['변동성', '차익실현', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3880</v>
+        <v>3855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.59%</t>
+          <t>+5.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>137600000000</v>
+        <v>138571000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 관련 언급과 함께 주가 상승에 대한 기대감 존재. 5G/6G 등 관련 이슈 언급.</t>
+          <t>빛과전자, 투기과열종목 회피 및 6G 관련 긍정적 전망. 15% 이상 상승 및 주포 움직임 주목.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투경 회피', '주가 상승', '이슈']</t>
+          <t>['투기과열종목', '6G', '주포']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6820</v>
+        <v>6740</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+4.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
         <v>336</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>14729000000</v>
+        <v>15064000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1846000</v>
+        <v>1850000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.96%</t>
+          <t>+3.18%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="F17" t="n">
         <v>457</v>
       </c>
       <c r="G17" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -1990,7 +1990,7 @@
         <v>50.66</v>
       </c>
       <c r="O17" t="n">
-        <v>3957607000000</v>
+        <v>4069925000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감이 높으며, 외인 매도와 관계없이 상승 추세를 예상하는 의견 다수. 일부 조정 가능성 언급.</t>
+          <t>SK하이닉스, 연기금 리밸런싱 및 외인 매도세 속 등락 전망. 대세 상승 인정 및 단기 급등 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상승 기대', '조정', '외인']</t>
+          <t>['연기금', '외인 매도', '대세 상승']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F18" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G18" t="n">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 및 웨스팅하우스 인수 관련 호재 언급. 상승 전망.</t>
+          <t>미국 원전 건설 프로젝트 및 웨스턴하우스 지분 인수 관련 호재 기대감. JP모건 리포트 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '미국', '호재']</t>
+          <t>['원전', '웨스턴하우스', 'JP모건']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G19" t="n">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 부정적 언급과 함께 '나락 차트', '축제 끝' 등 강한 부정적 표현 다수. 매도 의견 우세.</t>
+          <t>신규주 상승 패턴 언급 및 단기 급락 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['급락', '매도', '부정적']</t>
+          <t>['신규주', '급락', '패턴']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H20" t="n">
         <v>7.54</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각을 통한 주주환원 기대감 상승. 샘표와 비교하며 소각 규모 및 비율에 대한 논의.</t>
+          <t>자사주 매입 및 소각 이슈 부각. 주주환원 여력 충분, PBR 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['소각', '주주환원', '자사주']</t>
+          <t>['자사주 소각', '주주환원', 'PBR']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2329,10 +2329,10 @@
         <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H21" t="n">
         <v>5.86</v>
@@ -2424,7 +2424,7 @@
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>수주 기사 관련 언급 있으나 시장 반응 미미. 주가 상승 기대와 함께 담는 것이 좋다는 의견 존재. 구체적 사실 근거는 제한적.</t>
+          <t>호남 반도체 설계 용역 및 삼성 수주 관련 언급. 수주잔고 긍정적 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['수주', '주가 상승', '기대']</t>
+          <t>['수주', '반도체', '주주환원']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2510,13 +2510,13 @@
         <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
         <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H23" t="n">
         <v>4.91</v>
@@ -2542,7 +2542,7 @@
         <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>6394000000</v>
+        <v>6479000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>267000</v>
+        <v>268500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F24" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G24" t="n">
-        <v>1329</v>
+        <v>1373</v>
       </c>
       <c r="H24" t="n">
         <v>46.81</v>
@@ -2634,7 +2634,7 @@
         <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>2283898000000</v>
+        <v>2357091000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>정치적 언급이 주를 이루며, 삼성전자 자체에 대한 분석이나 전망은 미미. 자사주 매수 관련 긍정적 언급 소수 존재.</t>
+          <t>삼성전자, 자사주 15조 매수 및 배당 관련 소식에도 불구하고 투자자들의 정치적 이슈 언급 및 단기 등락 전망.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['자사주 매수', '정치']</t>
+          <t>['자사주 매수', '배당', '단기 전망']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18900</v>
+        <v>18980</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-5.36%</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>83555000000</v>
+        <v>85889000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2775,21 +2775,21 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3635</v>
+        <v>3645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.56%</t>
+          <t>-6.30%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
         <v>160</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>48737000000</v>
+        <v>48884000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>JW신약, 탈모 치료제 기대감 속 단기 조정 및 차트 이탈 우려. 분할 매수 및 단기 수익 가능성.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['탈모 치료제', '단기 조정', '분할 매수']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -2863,39 +2863,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>159</v>
+        <v>512</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-14.05%</t>
+          <t>-15.65%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E27" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>185</v>
+        <v>607</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.08</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>685000000</v>
+        <v>8334000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,11 +2935,11 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['급등', '거래량', '회생']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,46 +2948,46 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>006380</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>515</v>
+        <v>147</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-15.16%</t>
+          <t>-20.54%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.38</v>
+        <v>-0.01</v>
       </c>
       <c r="E28" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H28" t="n">
-        <v>2.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>607</v>
+        <v>185</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>0.08</v>
       </c>
       <c r="O28" t="n">
-        <v>8299000000</v>
+        <v>721000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['급등', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>006380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_13.xlsx
+++ b/data/trending_integrated_20260910_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4630</v>
+        <v>4440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+131.50%</t>
+          <t>+122.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G2" t="n">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>799352000000</v>
+        <v>820620000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 관련 업종 언급 있으나, 주가 흐름에 대한 기대와 우려가 혼재. 구체적인 사실 근거 부족.</t>
+          <t>합병 관련 업종에 대한 기대감과 불확실성이 공존. 극심한 변동성에 대한 경고.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩', '합병', '주가']</t>
+          <t>['합병', '신재생에너지', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8120</v>
+        <v>8160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+42.21%</t>
+          <t>+42.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" t="n">
-        <v>1418</v>
+        <v>1445</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>67504000000</v>
+        <v>67725000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
         <v>103</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14540</v>
+        <v>14560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.27%</t>
+          <t>+21.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="F5" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G5" t="n">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>289390000000</v>
+        <v>290605000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14195</v>
+        <v>14340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+20.19%</t>
+          <t>+21.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="H6" t="n">
         <v>6.09</v>
@@ -978,7 +978,7 @@
         <v>5.64</v>
       </c>
       <c r="O6" t="n">
-        <v>133739000000</v>
+        <v>139842000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3560</v>
+        <v>3655</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.08%</t>
+          <t>+21.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24618000000</v>
+        <v>24867000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>154600</v>
+        <v>12920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.03%</t>
+          <t>+12.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>407</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>184</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>1010</v>
+        <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>15.65</v>
+        <v>4.37</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138000</v>
+        <v>11530</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>15.25</v>
+        <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>373582000000</v>
+        <v>97034000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가 폭등', '매집', '단기 차별화']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12910</v>
+        <v>154100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.97%</t>
+          <t>+11.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>409</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="G9" t="n">
-        <v>47</v>
+        <v>1016</v>
       </c>
       <c r="H9" t="n">
-        <v>4.37</v>
+        <v>15.65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11530</v>
+        <v>138000</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.63</v>
+        <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>96659000000</v>
+        <v>377644000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['유가 폭등', '매집', '단기 차별화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,51 +1287,51 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14360</v>
+        <v>14960</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.37%</t>
+          <t>+9.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.53</v>
+        <v>1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>127</v>
+        <v>518</v>
       </c>
       <c r="H10" t="n">
-        <v>0.57</v>
+        <v>2.89</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13130</v>
+        <v>13700</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>116287000000</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,20 +1362,20 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>넥스틸, 중동 수출 가능성 언급 및 재무제표 기반 목표가 제시. 단기 변동성 후 상승 기대.</t>
+          <t>미국 광통신 시장 강세 및 AI 관련주 부각. 외인 매수세 유입으로 인한 상승 추세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['중동 수출', '재무제표', '목표가']</t>
+          <t>['광통신', 'AI', '외인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,46 +1384,46 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>092790</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14960</v>
+        <v>14270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+9.20%</t>
+          <t>+8.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.34</v>
+        <v>-0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>518</v>
+        <v>129</v>
       </c>
       <c r="H11" t="n">
-        <v>2.89</v>
+        <v>0.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13700</v>
+        <v>13130</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>117378000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,20 +1454,20 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 기대감. AI 관련주로 분류.</t>
+          <t>중동발 강관 수출 기대감 및 재무 구조 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['강관 수출', '재무 구조', '상승 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.92%</t>
+          <t>+8.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
         <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H12" t="n">
         <v>2.12</v>
@@ -1530,7 +1530,7 @@
         <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>189708000000</v>
+        <v>190580000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 매수세 지속에도 불구하고 주가 변동성이 큰 상황. 향후 주가 흐름에 대한 기대감 존재.</t>
+          <t>외인 매수세 유입에도 불구하고 변동성이 큰 흐름. 단기적인 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외국인', '변동성', '기대감']</t>
+          <t>['외인', '변동성', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,39 +1575,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2080</v>
+        <v>31100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+8.22%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
+        <v>12.31</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>28750</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.51</v>
+        <v>12.14</v>
       </c>
       <c r="O13" t="n">
-        <v>19885000000</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 새만금 및 반도체 테마 수혜 기대감 속 매집 흐름. 상한가 및 바닥 매수 권유.</t>
+          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['새만금', '반도체 테마', '매집']</t>
+          <t>['외국인 매도', '개인 매수', '차익실현']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,46 +1660,46 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31100</v>
+        <v>2070</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+7.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="H14" t="n">
-        <v>12.31</v>
+        <v>0.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>28750</v>
+        <v>1922</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12.14</v>
+        <v>0.51</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>19975000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,20 +1730,20 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>가온전선 상승 대비 대한전선 흐름 약세. 변동성 확대 및 차익 실현 가능성에 대한 부정적 전망.</t>
+          <t>강동씨앤엘, 새만금 및 반도체 테마 수혜 기대감 속 매집 흐름. 상한가 및 바닥 매수 권유.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['변동성', '차익실현', '주가']</t>
+          <t>['새만금', '반도체 테마', '매집']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3855</v>
+        <v>3875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+5.91%</t>
+          <t>+6.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>138571000000</v>
+        <v>139069000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>빛과전자, 투기과열종목 회피 및 6G 관련 긍정적 전망. 15% 이상 상승 및 주포 움직임 주목.</t>
+          <t>투경 회피 및 6G, 광통신 테마 관련 긍정적 전망. 주포의 움직임 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투기과열종목', '6G', '주포']</t>
+          <t>['투경 회피', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6740</v>
+        <v>6790</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+4.82%</t>
+          <t>+5.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H16" t="n">
         <v>15.68</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>15064000000</v>
+        <v>15390000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1850000</v>
+        <v>1857000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+3.18%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>796</v>
       </c>
       <c r="F17" t="n">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G17" t="n">
-        <v>2051</v>
+        <v>2135</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -1990,7 +1990,7 @@
         <v>50.66</v>
       </c>
       <c r="O17" t="n">
-        <v>4069925000000</v>
+        <v>4186701000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SK하이닉스, 연기금 리밸런싱 및 외인 매도세 속 등락 전망. 대세 상승 인정 및 단기 급등 기대.</t>
+          <t>네 마녀의 날 효과 및 일부 긍정적 전망에도 불구하고 외인 선물 매도세로 인한 변동성. 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['연기금', '외인 매도', '대세 상승']</t>
+          <t>['네 마녀의 날', '외인 매도', '상승 기대']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F18" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G18" t="n">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 프로젝트 및 웨스턴하우스 지분 인수 관련 호재 기대감. JP모건 리포트 언급.</t>
+          <t>미국 원전 건설 '팀코리아' 참여 및 웨스팅하우스 지분 인수 관련 호재. 최대 호재 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', 'JP모건']</t>
+          <t>['팀코리아', '원전 건설', '호재']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F19" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G19" t="n">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>신규주 상승 패턴 언급 및 단기 급락 우려.</t>
+          <t>개별 종목의 급락 및 단기 반등 예상, 그러나 투자자들의 혼란과 부정적 전망이 혼재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['신규주', '급락', '패턴']</t>
+          <t>['일봉', '급락', '반등']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H20" t="n">
         <v>7.54</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 이슈 부각. 주주환원 여력 충분, PBR 동반 상승 기대.</t>
+          <t>자사주 매입 및 소각 가능성에 대한 기대감으로 주가 상승 전망. 소각 비율 및 주주환원 여력에 대한 논의.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['자사주 소각', '주주환원', 'PBR']</t>
+          <t>['자사주 소각', '주주환원', '매입']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.32</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H21" t="n">
         <v>5.86</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F22" t="n">
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>호남 반도체 설계 용역 및 삼성 수주 관련 언급. 수주잔고 긍정적 전망.</t>
+          <t>수주 기사 및 삼성전자 수주 기반 긍정적 전망. 급등 준비 가능성 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['수주', '반도체', '주주환원']</t>
+          <t>['수주', '삼성전자', '급등 준비']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2155</v>
+        <v>269000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.04</v>
       </c>
       <c r="E23" t="n">
-        <v>97</v>
+        <v>793</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>465</v>
       </c>
       <c r="G23" t="n">
-        <v>179</v>
+        <v>1395</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>46.81</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2160</v>
+        <v>269500</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>46.85</v>
       </c>
       <c r="O23" t="n">
-        <v>6479000000</v>
+        <v>2463786000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,20 +2558,20 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>자사주 매입 및 배당 관련 긍정적 소식에도 불구하고 정치적 이슈와 불확실성으로 인한 보합세.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['자사주 매입', '배당', '불확실성']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>268500</v>
+        <v>2145</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.04</v>
+        <v>-0.35</v>
       </c>
       <c r="E24" t="n">
-        <v>791</v>
+        <v>98</v>
       </c>
       <c r="F24" t="n">
-        <v>471</v>
+        <v>45</v>
       </c>
       <c r="G24" t="n">
-        <v>1373</v>
+        <v>177</v>
       </c>
       <c r="H24" t="n">
-        <v>46.81</v>
+        <v>4.91</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>269500</v>
+        <v>2160</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>46.85</v>
+        <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>2357091000000</v>
+        <v>6532000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>삼성전자, 자사주 15조 매수 및 배당 관련 소식에도 불구하고 투자자들의 정치적 이슈 언급 및 단기 등락 전망.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['자사주 매수', '배당', '단기 전망']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18980</v>
+        <v>19050</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F25" t="n">
         <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>85889000000</v>
+        <v>89059000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차 해지 운동 관련 언급이 압도적. 주가 상승에 대한 기대감이 반영되었으나, 근거는 대차 해지에 집중.</t>
+          <t>대차 해지 운동 참여 독려와 함께 주주들의 부정적 심리 고조. 대규모 하락세.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차 해지', '주주 운동', '상승 기대']</t>
+          <t>['대차 해지', '부정적 심리', '하락세']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3645</v>
+        <v>3675</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.30%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>48884000000</v>
+        <v>49159000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>0.38</v>
       </c>
       <c r="E27" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H27" t="n">
         <v>2.8</v>
@@ -2910,7 +2910,7 @@
         <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>8334000000</v>
+        <v>8361000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>-0.01</v>
       </c>
       <c r="E28" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H28" t="n">
         <v>0.07000000000000001</v>

--- a/data/trending_integrated_20260910_13.xlsx
+++ b/data/trending_integrated_20260910_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4440</v>
+        <v>4240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+122.00%</t>
+          <t>+112.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="F2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G2" t="n">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>820620000000</v>
+        <v>840930000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 관련 업종에 대한 기대감과 불확실성이 공존. 극심한 변동성에 대한 경고.</t>
+          <t>합병 기대감과 투기적 움직임 혼재, 단기 급등락 가능성 높음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['합병', '신재생에너지', '변동성']</t>
+          <t>['스팩주', '합병', '단기급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G3" t="n">
-        <v>1445</v>
+        <v>1465</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>67725000000</v>
+        <v>67907000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
         <v>103</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14560</v>
+        <v>14380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.43%</t>
+          <t>+21.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>405</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
-        <v>467</v>
+        <v>675</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>6.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11990</v>
+        <v>11810</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>290605000000</v>
+        <v>146483000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>흥구석유, 중동 유가 급등 및 유조선 피격 관련 상승 기대. 단기 변동성 속 거래량 주목.</t>
+          <t>우리기술, 원전주로서 미국 신규 건설 및 공매도 금지 관련 긍정적 전망. 2만 원 목표 및 양전 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가 급등', '유조선 피격', '거래량']</t>
+          <t>['원전주', '신규 건설', '공매도 금지']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14340</v>
+        <v>14470</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+21.42%</t>
+          <t>+20.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>407</v>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="G6" t="n">
-        <v>652</v>
+        <v>468</v>
       </c>
       <c r="H6" t="n">
-        <v>6.09</v>
+        <v>0.03</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11810</v>
+        <v>11990</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>139842000000</v>
+        <v>292163000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>우리기술, 원전주로서 미국 신규 건설 및 공매도 금지 관련 긍정적 전망. 2만 원 목표 및 양전 기대.</t>
+          <t>흥구석유, 중동 유가 급등 및 유조선 피격 관련 상승 기대. 단기 변동성 속 거래량 주목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전주', '신규 건설', '공매도 금지']</t>
+          <t>['유가 급등', '유조선 피격', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1027,18 +1027,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3655</v>
+        <v>3540</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+21.23%</t>
+          <t>+17.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24867000000</v>
+        <v>26181000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12920</v>
+        <v>154100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.06%</t>
+          <t>+11.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>412</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>1021</v>
       </c>
       <c r="H8" t="n">
-        <v>4.37</v>
+        <v>15.65</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11530</v>
+        <v>138000</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.63</v>
+        <v>15.25</v>
       </c>
       <c r="O8" t="n">
-        <v>97034000000</v>
+        <v>380303000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['유가 폭등', '매집', '단기 차별화']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,43 +1195,43 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154100</v>
+        <v>12840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+11.67%</t>
+          <t>+11.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E9" t="n">
-        <v>409</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>184</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>1016</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
-        <v>15.65</v>
+        <v>4.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138000</v>
+        <v>11530</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>15.25</v>
+        <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>377644000000</v>
+        <v>97364000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 폭등 수혜 기대감 속 매집 흐름 관찰. 단기적 차별화 및 조정 가능성.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유가 폭등', '매집', '단기 차별화']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>1.34</v>
       </c>
       <c r="E10" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H10" t="n">
         <v>2.89</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 강세 및 AI 관련주 부각. 외인 매수세 유입으로 인한 상승 추세.</t>
+          <t>미국 광통신 관련주로 상승 추세 전망. 외국인 순매수세 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인 매수']</t>
+          <t>['광통신', 'AI', '외국인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14270</v>
+        <v>1912</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+8.68%</t>
+          <t>+8.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.53</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="H11" t="n">
-        <v>0.57</v>
+        <v>2.12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13130</v>
+        <v>1760</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>117378000000</v>
+        <v>190976000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>중동발 강관 수출 기대감 및 재무 구조 기반 상승 전망.</t>
+          <t>외인 매수세 유입 속 단기 급등락 반복, 전고점 돌파 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['강관 수출', '재무 구조', '상승 전망']</t>
+          <t>['종가배팅', '주포', '거래량']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>092790</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1912</v>
+        <v>14260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.64%</t>
+          <t>+8.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="H12" t="n">
-        <v>2.12</v>
+        <v>0.57</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1760</v>
+        <v>13130</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>190580000000</v>
+        <v>117814000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에도 불구하고 변동성이 큰 흐름. 단기적인 상승 기대감 존재.</t>
+          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인', '변동성', '기대감']</t>
+          <t>['중동', '강관', '재무재표']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2070</v>
+        <v>2045</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.70%</t>
+          <t>+6.40%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.34</v>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H14" t="n">
         <v>0.85</v>
@@ -1714,7 +1714,7 @@
         <v>0.51</v>
       </c>
       <c r="O14" t="n">
-        <v>19975000000</v>
+        <v>20188000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 새만금 및 반도체 테마 수혜 기대감 속 매집 흐름. 상한가 및 바닥 매수 권유.</t>
+          <t>새만금 및 건설 테마 관련 기대감, 기타법인 매도 물량 부담.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['새만금', '반도체 테마', '매집']</t>
+          <t>['새만금', '건설', '기타법인']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3875</v>
+        <v>3855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.46%</t>
+          <t>+5.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.62</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="H15" t="n">
         <v>1.57</v>
@@ -1806,7 +1806,7 @@
         <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>139069000000</v>
+        <v>139860000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투경 회피 및 6G, 광통신 테마 관련 긍정적 전망. 주포의 움직임 주시.</t>
+          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투경 회피', '6G', '광통신']</t>
+          <t>['투기과열', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6790</v>
+        <v>6710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+5.60%</t>
+          <t>+4.35%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16" t="n">
         <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H16" t="n">
         <v>15.68</v>
@@ -1898,7 +1898,7 @@
         <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>15390000000</v>
+        <v>15587000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1857000</v>
+        <v>1858000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F17" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G17" t="n">
-        <v>2135</v>
+        <v>2121</v>
       </c>
       <c r="H17" t="n">
         <v>50.67</v>
@@ -1990,7 +1990,7 @@
         <v>50.66</v>
       </c>
       <c r="O17" t="n">
-        <v>4186701000000</v>
+        <v>4284702000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>네 마녀의 날 효과 및 일부 긍정적 전망에도 불구하고 외인 선물 매도세로 인한 변동성. 상승 기대감 존재.</t>
+          <t>네 마녀의 날 앞두고 혼조세, 연기금 리밸런싱 및 외국인 움직임 주목.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['네 마녀의 날', '외인 매도', '상승 기대']</t>
+          <t>['네마녀의날', '리밸런싱', '외국인']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F18" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G18" t="n">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 참여 및 웨스팅하우스 지분 인수 관련 호재. 최대 호재 언급.</t>
+          <t>두산에너빌리티, 미국 원전 8기 건설 '팀코리아' 참여 및 웨스팅하우스 지분 인수 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['팀코리아', '원전 건설', '호재']</t>
+          <t>['원전', '팀코리아', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F19" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G19" t="n">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="H19" t="n">
         <v>0.33</v>
@@ -2234,13 +2234,13 @@
         <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="n">
         <v>7.54</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 가능성에 대한 기대감으로 주가 상승 전망. 소각 비율 및 주주환원 여력에 대한 논의.</t>
+          <t>자사주 매입 소각 가능성으로 인한 주가 상승 기대. 유통 물량 거래 활발.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['자사주 소각', '주주환원', '매입']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.32</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H21" t="n">
         <v>5.86</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
+          <t>시가총액 미달로 인한 상장폐지 위기. 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['상폐', '시가총액', '허매수']</t>
+          <t>['상장폐지', '시가총액', '주가']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>수주 기사 및 삼성전자 수주 기반 긍정적 전망. 급등 준비 가능성 언급.</t>
+          <t>수주 기사에도 불구하고 주가 부진. 개미 투자자 주의 촉구.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['수주', '삼성전자', '급등 준비']</t>
+          <t>['수주', '실적', '개미']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2510,13 +2510,13 @@
         <v>-0.04</v>
       </c>
       <c r="E23" t="n">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="F23" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G23" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="H23" t="n">
         <v>46.81</v>
@@ -2542,7 +2542,7 @@
         <v>46.85</v>
       </c>
       <c r="O23" t="n">
-        <v>2463786000000</v>
+        <v>2555443000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>자사주 매입 및 배당 관련 긍정적 소식에도 불구하고 정치적 이슈와 불확실성으로 인한 보합세.</t>
+          <t>이재명 관련 정치적 언급 다수, 자사주 매수 및 배당 관련 기대감 혼재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['자사주 매입', '배당', '불확실성']</t>
+          <t>['자사주매입', '배당', '정치']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2145</v>
+        <v>2130</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.35</v>
       </c>
       <c r="E24" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
         <v>177</v>
@@ -2634,7 +2634,7 @@
         <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>6532000000</v>
+        <v>6709000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19050</v>
+        <v>19100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F25" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" t="n">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>89059000000</v>
+        <v>92162000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차 해지 운동 참여 독려와 함께 주주들의 부정적 심리 고조. 대규모 하락세.</t>
+          <t>대차해지 운동 집중, 미국 투자 및 원전 이슈 관련 기대감.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차 해지', '부정적 심리', '하락세']</t>
+          <t>['대차해지', '미국 투자', '원전']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2786,13 +2786,13 @@
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>49159000000</v>
+        <v>49336000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>JW신약, 탈모 치료제 기대감 속 단기 조정 및 차트 이탈 우려. 분할 매수 및 단기 수익 가능성.</t>
+          <t>탈모 치료제 기대감 속 주가 변동성 확대, 차트 붕괴 및 나락 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '단기 조정', '분할 매수']</t>
+          <t>['탈모', '신고가', '차트']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-15.65%</t>
+          <t>-15.82%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0.38</v>
       </c>
       <c r="E27" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H27" t="n">
         <v>2.8</v>
@@ -2910,7 +2910,7 @@
         <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>8361000000</v>
+        <v>8447000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>-0.01</v>
       </c>
       <c r="E28" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H28" t="n">
         <v>0.07000000000000001</v>
